--- a/esthetician_forms/009_grooming_appointment_form--esthetician_forms.xlsx
+++ b/esthetician_forms/009_grooming_appointment_form--esthetician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'hair_cut',_'label':_'hair_cut',_'value':_'hair_cut'}</t>
+          <t>hair_cut</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'hair_cut', 'label': 'Hair Cut', 'value': 'Hair Cut'}</t>
+          <t>Hair Cut</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'nail_service',_'label':_'nail_service',_'value':_'nail_service'}</t>
+          <t>nail_service</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'nail_service', 'label': 'Nail Service', 'value': 'Nail Service'}</t>
+          <t>Nail Service</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'massage',_'label':_'massage',_'value':_'massage'}</t>
+          <t>massage</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'massage', 'label': 'Massage', 'value': 'Massage'}</t>
+          <t>Massage</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'facial',_'label':_'facial',_'value':_'facial'}</t>
+          <t>facial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'facial', 'label': 'Facial', 'value': 'Facial'}</t>
+          <t>Facial</t>
         </is>
       </c>
     </row>
